--- a/Silver/lld/DCST/attr_DCST_THONG_TIN_DK_THUE.xlsx
+++ b/Silver/lld/DCST/attr_DCST_THONG_TIN_DK_THUE.xlsx
@@ -1,7 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registered Taxpayer" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP Postal Address" sheetId="2" state="visible" r:id="rId2"/>
@@ -9,30 +13,45 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP Alt Identification" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -40,17 +59,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -197,7 +228,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -232,7 +262,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,16 +296,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -398,46 +431,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -451,1383 +445,1475 @@
   <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.83203125" customWidth="1" min="1" max="1"/>
-    <col width="30.83203125" customWidth="1" min="2" max="2"/>
-    <col width="20.83203125" customWidth="1" min="3" max="3"/>
-    <col width="10.83203125" customWidth="1" min="4" max="4"/>
-    <col width="14.83203125" customWidth="1" min="5" max="5"/>
-    <col width="10.83203125" customWidth="1" min="6" max="6"/>
-    <col width="45.83203125" customWidth="1" min="7" max="7"/>
-    <col width="40.83203125" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>attribute_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>data_domain</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nullable</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_primary_key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>source_columns</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Registered Taxpayer Id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Id tự sinh (surrogate key)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Surrogate Key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PK surrogate</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>PK surrogate. BCV: không có term "Registered Taxpayer" riêng. Gần nhất: "Organization Tax Identification Number" (Involved Party) — mô tả số thuế, không phải entity. Team đặt "Registered Taxpayer" theo HLD — mô tả tổ chức/DN đã đăng ký thuế với TCT.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Registered Taxpayer Code</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>ID bản ghi nguồn. Mã định danh bản ghi đăng ký thuế (BK)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.ID</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>BK chính. PK của bảng nguồn</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Source System Code</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Mã nguồn dữ liệu. Giá trị: DCST.THONG_TIN_DK_THUE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>BK. Hardcode</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Tax Identification Number</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Mã số thuế</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.MA_SO_THUE</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Trường liên kết ngầm với DN_RUI_RO_CAO, cưỡng chế... Unique nhưng không phải BK</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Organization Tax Identification Number" (Involved Party) — "Identifies the number which uniquely identifies the Organization to the tax authorities." Bỏ prefix "Organization" vì scope bảng nguồn bao gồm cả hộ KD (không chỉ tổ chức). Trường liên kết ngầm với DN_RUI_RO_CAO, cưỡng chế... Unique nhưng không phải BK.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Batch Id</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>ID gói tin. Mã gói tin truyền nhận dữ liệu từ TCT</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.GOI_TIN_ID</t>
         </is>
       </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Metadata truyền nhận — thiết kế thành trường nghiệp vụ bình thường (không đưa vào ds_). Đặt "Batch Id" theo quy ước dự án cho trường metadata gói tin.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Tên người nộp thuế</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TEN_NGUOI_NOP</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Full Name" (Involved Party) — "Identifies the entire and complete name of the Involved Party." Giữ nguyên BCV term. Không thêm prefix "Organization" vì scope bao gồm cả hộ KD.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Charter Capital Amount</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Vốn điều lệ</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Currency Amount</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.VON_DIEU_LE</t>
         </is>
       </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term "Charter Capital" riêng. Gần nhất: concept tài chính Organization nhưng BCV tập trung vào banking, không có thuật ngữ vốn điều lệ. Đặt "Charter Capital Amount" theo thuật ngữ pháp lý VN. Suffix Amount theo Data Domain = Currency Amount.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Charter Capital Currency Code</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Loại tiền vốn điều lệ</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.LOAITIEN_VON_DL_VN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>FK → bảng Currency (SCD1)</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Currency Code" (Common) — "A standard code to represent a currency." Thêm prefix "Charter Capital" để phân biệt với Foreign Charter Capital Currency Code. FK → bảng Currency (SCD1).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Foreign Charter Capital Amount</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Vốn điều lệ nước ngoài</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Currency Amount</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.SOTIEN_VON_DL_NN</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đặt tên đối xứng với Charter Capital Amount, thêm prefix "Foreign".</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Foreign Charter Capital Currency Code</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Loại tiền vốn điều lệ nước ngoài</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.LOAITIEN_VON_DL_NN</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>FK → bảng Currency (SCD1)</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Currency Code" (Common). Tương tự Charter Capital Currency Code, thêm prefix "Foreign". FK → bảng Currency (SCD1).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Industry Classification Code</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Mã ngành nghề kinh doanh</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.MA_NGANH</t>
         </is>
       </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Organization Industry Classification" (Involved Party) + "Industry Classification Code" (Common) — "The Code assigned to the Industry Classification." Bỏ prefix "Organization" (lý do scope). Suffix Code theo Data Domain = Classification Value.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Industry Classification Description</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Ngành nghề kinh doanh</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.NGANH_NGHE_KD</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Mô tả dạng text tự do</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Industry Classification Description" (Common) — "Description provides a textual explanation or free form comments about the Industry Classification." Giữ nguyên BCV term. Mô tả dạng text tự do từ nguồn.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Business Commencement Date</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Ngày bắt đầu hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.NGAY_BD_HDKD</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Khác Establish Date — ngày bắt đầu KD thực tế</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>BCV: gần nhất "Organization Incorporation Date" — "Identifies the date of the Incorporation of the Organization." Không dùng "Incorporation Date" vì nghĩa khác: incorporation = thành lập pháp nhân, commencement = bắt đầu KD thực tế. Đặt "Business Commencement Date" theo đúng nghĩa nguồn.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Parent Organization Name</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Đơn vị chủ quan/ đơn vị quản lý trực thuộc</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.DON_VI_CHU_QUAN</t>
         </is>
       </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Parent Organization" (Involved Party) — "Identifies the parent Organization who owns 50% or more of the Subsidiary." BCV mô tả công ty mẹ sở hữu &gt;50%. Nguồn mô tả "đơn vị chủ quản" — nghĩa rộng hơn nhưng cùng concept. Giữ "Parent Organization Name" — suffix Name vì chỉ lưu tên text, không FK.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Parent Organization Address</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Địa chỉ đơn vị chủ quản</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.DVCQ_VN_DIACHI</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Text tự do, không đủ cấu trúc tách Postal Address</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term "Parent Organization Address" riêng. Đặt tên theo pattern [Parent Organization] + Address. Text tự do, không đủ cấu trúc tách Postal Address.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Direct Managing Authority Name</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Cơ quan quản lý trực tiếp</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.CO_QUAN_QUAN_LY_TRUC_TIEP</t>
         </is>
       </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đặt "Direct Managing Authority Name" dịch sát nghĩa nguồn "cơ quan quản lý trực tiếp". Suffix Name vì chỉ lưu tên text.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Tax Authority Code</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Mã cơ quan quản lý thuế</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.MA_CQQL_QLT</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Cần xác nhận có danh mục chuẩn không</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng cho cơ quan thuế. Đặt "Tax Authority Code" theo ngữ cảnh thuế. Suffix Code theo Data Domain = Classification Value. Cần xác nhận có danh mục chuẩn không.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Operating Status Code</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Trạng thái hoạt động: 00, 04: Đang hoạt động; 01: Ngừng HĐ + hoàn thành thủ tục; 03: Ngừng HĐ + chưa hoàn thành; 05: Ngừng KD có thời hạn; 06: Không HĐ tại địa chỉ ĐK</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TRANG_THAI_HOAT_DONG</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Classification Type = TAXPAYER_OPERATING_STATUS</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>BCV: gần nhất "Life Cycle Status" pattern (có cho mọi entity). Không dùng "Life Cycle Status" vì nguồn mô tả trạng thái hoạt động kinh doanh (operating), không phải vòng đời entity trên model. Đặt "Operating Status Code" dịch sát nghĩa nguồn. Classification Type = TAXPAYER_OPERATING_STATUS.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Cessation Reason Description</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Lý do ngừng hoạt động</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.LY_DO_NGUNG_HOAT_DONG</t>
         </is>
       </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>BCV: gần nhất "Life Cycle Status Reason" pattern. Không dùng vì lý do tương tự Operating Status. Đặt "Cessation Reason Description" — "Cessation" = ngừng hoạt động. Suffix Description vì text tự do, không phải mã phân loại.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Cessation Type Code</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Loại ngừng hoạt động: 1. Giải thể; 2. Phá sản; 3. Chuyển đổi loại hình DN; 4. Cho làm thủ tục giải thể; 5. Phá sản; 6. Tổ chức lại; 7. Thu hồi GP; 8. Đóng theo ĐV chủ quản; 9. Khác</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.LOAI_NGUNG_HOAT_DONG</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Classification Type = TAXPAYER_CESSATION_TYPE</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đặt "Cessation Type Code" — phân loại lý do ngừng. Suffix Code theo Data Domain. Classification Type = TAXPAYER_CESSATION_TYPE.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Cessation Date</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Ngày ngừng hoạt động</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.NGUNG_HD_NGAY</t>
         </is>
       </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đặt "Cessation Date" nhất quán prefix "Cessation" với các trường cùng nhóm.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Cessation Detail Reason Description</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Lý do ngừng hoạt động (chi tiết)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.NGUNG_HD_LY_DO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Cần xác nhận khác biệt với LY_DO_NGUNG_HOAT_DONG. Nếu trùng → bỏ 1</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Thêm "Detail" phân biệt với Cessation Reason Description (LY_DO_NGUNG_HOAT_DONG). Cần xác nhận khác biệt với LY_DO_NGUNG_HOAT_DONG. Nếu trùng → bỏ 1.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Cessation Note</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Ghi chú ngừng hoạt động</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.NGUNG_HD_GHI_CHU</t>
         </is>
       </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đặt "Cessation Note" — suffix Note cho trường ghi chú tự do.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Cessation Notice Number</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Số thông báo ngừng hoạt động</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.NGUNG_HD_SO_TBAO</t>
         </is>
       </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đặt "Cessation Notice Number" — "Notice" = thông báo hành chính, "Number" = số hiệu văn bản.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Suspension Start Date</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Tạm nghỉ/Từ ngày</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TAM_NGHI_TU_NGAY</t>
         </is>
       </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đặt "Suspension" = tạm nghỉ (khác "Cessation" = ngừng hẳn). Suffix Start Date / End Date theo pattern thời gian hiệu lực.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Suspension End Date</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Tạm nghỉ/Đến ngày</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TAM_NGHI_DEN_NGAY</t>
         </is>
       </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đối xứng với Suspension Start Date.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Suspension Reason Description</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Lý do tạm nghỉ</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TAM_NGHI_LY_DO</t>
         </is>
       </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Pattern [Nhóm] + Reason Description — nhất quán với Cessation Reason Description.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Suspension Notice Number</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Số thông báo - tạm nghỉ</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TAM_NGHI_SO_TBAO</t>
         </is>
       </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Pattern [Nhóm] + Notice Number — nhất quán với Cessation Notice Number.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Suspension Notice Date</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Ngày thông báo - tạm nghỉ</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TAM_NGHI_NGAY_TB_NNT</t>
         </is>
       </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term riêng. Đặt "Suspension Notice Date" — ngày ban hành thông báo tạm nghỉ.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Legal Representative Name</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Tên người đại diện kinh doanh</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TEN_NGUOI_DAI_DIEN_KD</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Giữ dạng text denormalized — không có cơ chế link sang TTKDT_NGUOI_DAI_DIEN</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Legal Representative" (Involved Party) — "Identifies an Individual who acts in a legal capacity." Giữ dạng text denormalized — không có cơ chế link sang TTKDT_NGUOI_DAI_DIEN (trường này ghi tên người ĐD pháp luật, bảng con TTKDT_NGUOI_DAI_DIEN ghi chi tiết từng người ĐD — 2 nguồn khác nhau). Suffix Name vì text.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Legal Representative Identification Number</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Số CMT/ hộ chiếu người đại diện theo pháp luật/ chủ doanh nghiệp tư nhân</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.SO_CMT</t>
         </is>
       </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Individual Tax Identification Number" mô tả mã thuế cá nhân — không đúng ngữ cảnh. Gần hơn: "Involved Party Alternative Identification" (concept giấy tờ tùy thân). Đặt "Legal Representative Identification Number" — prefix "Legal Representative" xác định chủ thể, suffix "Identification Number" nhất quán M9.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Legal Representative Phone Number</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Số ĐT người đại diện theo pháp luật/ chủ doanh nghiệp tư nhân</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.SO_DIEN_THOAI</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Thông tin của người, không phải DN → không tách ra Electronic Address</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Electronic Address" (Location). Không tách ra IP Electronic Address vì đây là thông tin của người (cá nhân), không phải DN. Giữ denormalized tại entity chính. Suffix "Phone Number" tường minh.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Director Name</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Tên giám đốc/ tổng giám đốc</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.TEN_GIAM_DOC</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Người khác với người ĐD pháp luật</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term "Director" riêng. Gần nhất: "Legal Representative" — nhưng GĐ có thể khác người ĐD pháp luật. Đặt "Director Name" dịch sát nghĩa nguồn. Giữ denormalized — cùng pattern với Legal Representative Name.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Director Phone Number</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Số điện thoại giám đốc/ tổng giám đốc</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.SO_DIEN_THOAI_GD</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Electronic Address" (Location). Không tách ra IP Electronic Address — thông tin cá nhân GĐ. Pattern đối xứng với Legal Representative Phone Number.</t>
         </is>
       </c>
     </row>
@@ -1845,381 +1931,383 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.83203125" customWidth="1" min="1" max="1"/>
-    <col width="30.83203125" customWidth="1" min="2" max="2"/>
-    <col width="20.83203125" customWidth="1" min="3" max="3"/>
-    <col width="10.83203125" customWidth="1" min="4" max="4"/>
-    <col width="14.83203125" customWidth="1" min="5" max="5"/>
-    <col width="10.83203125" customWidth="1" min="6" max="6"/>
-    <col width="45.83203125" customWidth="1" min="7" max="7"/>
-    <col width="40.83203125" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>attribute_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>data_domain</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nullable</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_primary_key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>source_columns</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Involved Party Id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FK đến Registered Taxpayer</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Surrogate Key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.ID</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FK. Resolve qua Registered Taxpayer Id</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>FK. Resolve qua Registered Taxpayer Id. Shared entity — không có PK surrogate riêng.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Involved Party Code</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Mã người nộp thuế</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.ID</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Pattern Id + Code</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Source System Code</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Mã nguồn dữ liệu. Giá trị: DCST.THONG_TIN_DK_THUE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Hardcode</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Address Type Code</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Loại địa chỉ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ETL derive: HEAD_OFFICE hoặc BUSINESS</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term "Address Type" riêng (BCV phân loại qua relationship, không qua type code). Đặt theo quy ước dự án shared entity. ETL derive: HEAD_OFFICE hoặc BUSINESS.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Address Line</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Địa chỉ trụ sở chính / Mô tả địa chỉ kinh doanh</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.DIA_CHI_TSC|DCST.dbo.THONG_TIN_DK_THUE.MOTA_DIACHI_KD</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>HEAD_OFFICE ← DIA_CHI_TSC; BUSINESS ← MOTA_DIACHI_KD</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>BCV: gần nhất "Postal Address" / "Address" (Location concept). Đặt "Address Line" theo quy ước dự án — gộp địa chỉ thành text line. HEAD_OFFICE ← DIA_CHI_TSC; BUSINESS ← MOTA_DIACHI_KD.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Province Code</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Mã tỉnh - kinh doanh</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.MA_TINH_KD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Chỉ có cho BUSINESS. HEAD_OFFICE = NULL</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Province" (Location) — "Identifies a Geographic Area that is a political subdivision of a country." Cũng có "Address Province" — "Identifies the Province associated with the Address." Đặt "Province Code" rút gọn. Suffix Code. Chỉ có cho BUSINESS. HEAD_OFFICE = NULL.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>District Code</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Mã huyện - kinh doanh</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.MA_HUYEN_KD</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Chỉ có cho BUSINESS</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "District" (Location) — "Identifies a Geographic Area that is an administrative or political division of a territory." Cũng có "Address District". Đặt "District Code" rút gọn. Chỉ có cho BUSINESS.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Mã xã - kinh doanh</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.MA_XA_KD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Chỉ có cho BUSINESS</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term "Ward" riêng (BCV quốc tế không có cấp xã/phường). Đặt "Ward Code" theo đơn vị hành chính VN. Chỉ có cho BUSINESS.</t>
         </is>
       </c>
     </row>
@@ -2237,255 +2325,257 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.83203125" customWidth="1" min="1" max="1"/>
-    <col width="30.83203125" customWidth="1" min="2" max="2"/>
-    <col width="20.83203125" customWidth="1" min="3" max="3"/>
-    <col width="10.83203125" customWidth="1" min="4" max="4"/>
-    <col width="14.83203125" customWidth="1" min="5" max="5"/>
-    <col width="10.83203125" customWidth="1" min="6" max="6"/>
-    <col width="45.83203125" customWidth="1" min="7" max="7"/>
-    <col width="40.83203125" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>attribute_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>data_domain</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nullable</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_primary_key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>source_columns</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Involved Party Id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FK đến Registered Taxpayer</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Surrogate Key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.ID</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FK</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>FK. Shared entity — không có PK surrogate riêng.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Involved Party Code</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Mã người nộp thuế</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.ID</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Pattern Id + Code</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Source System Code</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Mã nguồn dữ liệu. Giá trị: DCST.THONG_TIN_DK_THUE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Hardcode</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Electronic Address Type Code</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Loại kênh liên lạc</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ETL derive: PHONE_HEAD_OFFICE, FAX_HEAD_OFFICE, PHONE_BUSINESS, EMAIL_BUSINESS, FAX_BUSINESS. Tối đa 5 dòng/DN</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Electronic Address" (Location) — "Identifies an Address that is a logical entry point into an electronic delivery system." Đặt "Electronic Address Type Code" theo BCV concept + suffix Type Code để phân loại kênh. ETL derive: PHONE_HEAD_OFFICE, FAX_HEAD_OFFICE, PHONE_BUSINESS, EMAIL_BUSINESS, FAX_BUSINESS. Tối đa 5 dòng/DN.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Electronic Address Value</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Điện thoại / Fax / Email. Giá trị kênh liên lạc của DN</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.DIEN_THOAI|DCST.dbo.THONG_TIN_DK_THUE.FAX|DCST.dbo.THONG_TIN_DK_THUE.DIEN_THOAI_KD|DCST.dbo.THONG_TIN_DK_THUE.EMAIL_KD|DCST.dbo.THONG_TIN_DK_THUE.FAX_KD</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Mỗi trường nguồn tạo 1 dòng với Address Type tương ứng</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Electronic Address" (Location). Đặt "Electronic Address Value" — suffix Value chứa giá trị thực tế. Mỗi trường nguồn tạo 1 dòng với Address Type tương ứng.</t>
         </is>
       </c>
     </row>
@@ -2503,339 +2593,341 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.83203125" customWidth="1" min="1" max="1"/>
-    <col width="30.83203125" customWidth="1" min="2" max="2"/>
-    <col width="20.83203125" customWidth="1" min="3" max="3"/>
-    <col width="10.83203125" customWidth="1" min="4" max="4"/>
-    <col width="14.83203125" customWidth="1" min="5" max="5"/>
-    <col width="10.83203125" customWidth="1" min="6" max="6"/>
-    <col width="45.83203125" customWidth="1" min="7" max="7"/>
-    <col width="40.83203125" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>attribute_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>data_domain</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nullable</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>is_primary_key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>source_columns</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Involved Party Id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FK đến Registered Taxpayer</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Surrogate Key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.ID</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>FK</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>FK. Shared entity — không có PK surrogate riêng.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Involved Party Code</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Mã người nộp thuế</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.ID</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Pattern Id + Code</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Source System Code</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Mã nguồn dữ liệu. Giá trị: DCST.THONG_TIN_DK_THUE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Hardcode</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Identification Type Code</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Loại giấy tờ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Classification Value</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>BUSINESS_LICENSE hoặc ESTABLISHMENT_DECISION. Tối đa 2 dòng/DN</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Involved Party Alternative Identification Type" (Involved Party) — "Distinguishes between Alternative Identifications according to the different types." Rút gọn bỏ prefix "Involved Party Alternative" (đã nằm trong entity name). Thêm suffix Code. Nhất quán với M9 Case Study Customer. BUSINESS_LICENSE hoặc ESTABLISHMENT_DECISION. Tối đa 2 dòng/DN.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Identification Number</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Số giấy phép thành lập / Số quyết định thành lập</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.SO_GIAY_PHEP|DCST.dbo.THONG_TIN_DK_THUE.SO_QUYET_DINH</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>BUSINESS_LICENSE ← SO_GIAY_PHEP; ESTABLISHMENT_DECISION ← SO_QUYET_DINH</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Involved Party Alternative Identification" (Involved Party) — concept giấy tờ định danh. Cũng có "Certificate Of Incorporation" (Documentation) — "documents the establishment of a corporate body." Đặt "Identification Number" theo quy ước dự án nhất quán M9. BUSINESS_LICENSE ← SO_GIAY_PHEP; ESTABLISHMENT_DECISION ← SO_QUYET_DINH.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Issue Date</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Ngày cấp / Ngày ban hành quyết định</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.NGAY_CAP|DCST.dbo.THONG_TIN_DK_THUE.NGAY_BAN_HANH</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>BUSINESS_LICENSE ← NGAY_CAP; ESTABLISHMENT_DECISION ← NGAY_BAN_HANH</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>BCV: "Registration Documentation Issue Date" (Documentation) — "Identifies the date on which the Registration Authority issued the Registration." Rút gọn thành "Issue Date" — không prefix loại giấy tờ vì Identification Type Code đã phân biệt. Nhất quán với shared entity pattern. BUSINESS_LICENSE ← NGAY_CAP; ESTABLISHMENT_DECISION ← NGAY_BAN_HANH.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Issuing Authority Name</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Cơ quan cấp giấy phép thành lập / Cơ quan ban hành quyết định thành lập</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>DCST.dbo.THONG_TIN_DK_THUE.CO_QUAN_CAP|DCST.dbo.THONG_TIN_DK_THUE.CO_QUAN_BAN_HANH</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>BUSINESS_LICENSE ← CO_QUAN_CAP; ESTABLISHMENT_DECISION ← CO_QUAN_BAN_HANH</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>BCV: không có term "Issuing Authority" riêng. Gần nhất: "Industry Classification Definer" — concept cơ quan ban hành, nhưng khác ngữ cảnh. Đặt "Issuing Authority Name" — "Issuing Authority" phổ biến trong banking (ISO 20022 dùng). Suffix Name vì text. BUSINESS_LICENSE ← CO_QUAN_CAP; ESTABLISHMENT_DECISION ← CO_QUAN_BAN_HANH.</t>
         </is>
       </c>
     </row>
